--- a/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
+++ b/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
+++ b/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
+++ b/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -105,16 +105,22 @@
     <t>POST</t>
   </si>
   <si>
+    <t>HTTP POST Command.</t>
+  </si>
+  <si>
     <t>PUT</t>
   </si>
   <si>
+    <t>HTTP PUT Command.</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/http-verb</t>
+    <t>http://hl7.org/fhir/http-verb</t>
   </si>
 </sst>
 </file>
@@ -397,28 +403,32 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
+++ b/testbuild/ValueSet-pmd-bundle-requests.valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.1</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
